--- a/backend/data/puntos.xlsx
+++ b/backend/data/puntos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\sig\proyecto\Documentos\Datos_Lineas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3439877-9BC4-41E2-AF79-B820CC9D5AAC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E3C477-310D-43C3-A5CA-BCEDC9649CFB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
